--- a/taifex_summary.xlsx
+++ b/taifex_summary.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU17"/>
+  <dimension ref="A1:AU18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2488,6 +2488,153 @@
         <v>1460.71</v>
       </c>
     </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/07</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n">
+        <v>20333</v>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>71465</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>-51132</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>-433157920</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>-165</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>-400424</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>-606575276</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>1393</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>2302</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>174.13</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>118801</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>68224</v>
+      </c>
+      <c r="N18" s="10" t="n">
+        <v>43000</v>
+      </c>
+      <c r="O18" s="10" t="n">
+        <v>196</v>
+      </c>
+      <c r="P18" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="Q18" s="10" t="n">
+        <v>717</v>
+      </c>
+      <c r="R18" s="10" t="n">
+        <v>41500</v>
+      </c>
+      <c r="S18" s="10" t="n">
+        <v>44900</v>
+      </c>
+      <c r="T18" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="U18" s="10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="X18" s="10" t="n">
+        <v>43000</v>
+      </c>
+      <c r="Y18" s="8" t="n">
+        <v>196</v>
+      </c>
+      <c r="Z18" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AA18" s="8" t="n">
+        <v>717</v>
+      </c>
+      <c r="AB18" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AC18" s="10" t="n">
+        <v>1281</v>
+      </c>
+      <c r="AD18" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AE18" s="10" t="n">
+        <v>2476</v>
+      </c>
+      <c r="AF18" s="10" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AG18" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="AH18" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AI18" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AJ18" s="8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AK18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL18" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AM18" s="8" t="n">
+        <v>1281</v>
+      </c>
+      <c r="AN18" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AO18" s="8" t="n">
+        <v>2476</v>
+      </c>
+      <c r="AP18" s="10" t="inlineStr">
+        <is>
+          <t>短多長空、多頭一致</t>
+        </is>
+      </c>
+      <c r="AQ18" s="8" t="n">
+        <v>464.12</v>
+      </c>
+      <c r="AR18" s="8" t="n">
+        <v>150.52</v>
+      </c>
+      <c r="AS18" s="9" t="n">
+        <v>-41.42</v>
+      </c>
+      <c r="AT18" s="10" t="n">
+        <v>573.22</v>
+      </c>
+      <c r="AU18" s="8" t="n">
+        <v>1924.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/taifex_summary.xlsx
+++ b/taifex_summary.xlsx
@@ -873,7 +873,7 @@
         <v>32000</v>
       </c>
       <c r="V2" s="8" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="W2" s="8" t="n">
         <v>10.7</v>
@@ -897,28 +897,28 @@
         <v>1998</v>
       </c>
       <c r="AD2" s="10" t="n">
-        <v>26500</v>
+        <v>30000</v>
       </c>
       <c r="AE2" s="10" t="n">
-        <v>7317</v>
+        <v>2006</v>
       </c>
       <c r="AF2" s="10" t="n">
-        <v>33800</v>
+        <v>33600</v>
       </c>
       <c r="AG2" s="10" t="n">
-        <v>38000</v>
+        <v>35500</v>
       </c>
       <c r="AH2" s="10" t="n">
-        <v>26500</v>
+        <v>29500</v>
       </c>
       <c r="AI2" s="10" t="n">
-        <v>33000</v>
+        <v>34400</v>
       </c>
       <c r="AJ2" s="8" t="n">
-        <v>8.1</v>
+        <v>14.9</v>
       </c>
       <c r="AK2" s="8" t="n">
-        <v>23.1</v>
+        <v>11.2</v>
       </c>
       <c r="AL2" s="10" t="n">
         <v>35000</v>
@@ -927,14 +927,14 @@
         <v>1998</v>
       </c>
       <c r="AN2" s="10" t="n">
-        <v>26500</v>
+        <v>30000</v>
       </c>
       <c r="AO2" s="8" t="n">
-        <v>7317</v>
+        <v>2006</v>
       </c>
       <c r="AP2" s="10" t="inlineStr">
         <is>
-          <t>短空長多、短多長空</t>
+          <t>短空長多、空頭一致</t>
         </is>
       </c>
       <c r="AQ2" s="10" t="n"/>
@@ -985,95 +985,35 @@
       <c r="M3" s="10" t="n">
         <v>76587</v>
       </c>
-      <c r="N3" s="10" t="n">
-        <v>33000</v>
-      </c>
-      <c r="O3" s="10" t="n">
-        <v>2891</v>
-      </c>
-      <c r="P3" s="10" t="n">
-        <v>29300</v>
-      </c>
-      <c r="Q3" s="10" t="n">
-        <v>5210</v>
-      </c>
-      <c r="R3" s="10" t="n">
-        <v>32500</v>
-      </c>
-      <c r="S3" s="10" t="n">
-        <v>35500</v>
-      </c>
-      <c r="T3" s="10" t="n">
-        <v>29300</v>
-      </c>
-      <c r="U3" s="10" t="n">
-        <v>32000</v>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W3" s="8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="X3" s="10" t="n">
-        <v>33000</v>
-      </c>
-      <c r="Y3" s="8" t="n">
-        <v>2891</v>
-      </c>
-      <c r="Z3" s="10" t="n">
-        <v>29300</v>
-      </c>
-      <c r="AA3" s="8" t="n">
-        <v>5210</v>
-      </c>
-      <c r="AB3" s="10" t="n">
-        <v>35000</v>
-      </c>
-      <c r="AC3" s="10" t="n">
-        <v>2135</v>
-      </c>
-      <c r="AD3" s="10" t="n">
-        <v>26500</v>
-      </c>
-      <c r="AE3" s="10" t="n">
-        <v>7430</v>
-      </c>
-      <c r="AF3" s="10" t="n">
-        <v>33800</v>
-      </c>
-      <c r="AG3" s="10" t="n">
-        <v>38000</v>
-      </c>
-      <c r="AH3" s="10" t="n">
-        <v>26500</v>
-      </c>
-      <c r="AI3" s="10" t="n">
-        <v>33000</v>
-      </c>
-      <c r="AJ3" s="8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AK3" s="8" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="AL3" s="10" t="n">
-        <v>35000</v>
-      </c>
-      <c r="AM3" s="8" t="n">
-        <v>2135</v>
-      </c>
-      <c r="AN3" s="10" t="n">
-        <v>26500</v>
-      </c>
-      <c r="AO3" s="8" t="n">
-        <v>7430</v>
-      </c>
-      <c r="AP3" s="10" t="inlineStr">
-        <is>
-          <t>短空長多、短多長空</t>
-        </is>
-      </c>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="10" t="n"/>
+      <c r="AI3" s="10" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="10" t="n"/>
+      <c r="AO3" s="10" t="n"/>
+      <c r="AP3" s="10" t="n"/>
       <c r="AQ3" s="10" t="n"/>
       <c r="AR3" s="10" t="n"/>
       <c r="AS3" s="10" t="n"/>
@@ -1301,10 +1241,10 @@
         <v>37000</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>40000</v>
@@ -1325,28 +1265,28 @@
         <v>1620</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>26900</v>
+        <v>34300</v>
       </c>
       <c r="AE6" s="10" t="n">
-        <v>4159</v>
+        <v>1658</v>
       </c>
       <c r="AF6" s="10" t="n">
-        <v>32500</v>
+        <v>35500</v>
       </c>
       <c r="AG6" s="10" t="n">
-        <v>40800</v>
+        <v>40000</v>
       </c>
       <c r="AH6" s="10" t="n">
-        <v>26900</v>
+        <v>33500</v>
       </c>
       <c r="AI6" s="10" t="n">
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="AJ6" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="AK6" s="8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="AL6" s="10" t="n">
         <v>38000</v>
@@ -1355,10 +1295,10 @@
         <v>1620</v>
       </c>
       <c r="AN6" s="10" t="n">
-        <v>26900</v>
+        <v>34300</v>
       </c>
       <c r="AO6" s="8" t="n">
-        <v>4159</v>
+        <v>1658</v>
       </c>
       <c r="AP6" s="10" t="inlineStr">
         <is>
@@ -1740,7 +1680,7 @@
         <v>42900</v>
       </c>
       <c r="T11" s="10" t="n">
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="U11" s="10" t="n">
         <v>39000</v>
@@ -1749,7 +1689,7 @@
         <v>20.6</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X11" s="10" t="n">
         <v>42500</v>
@@ -1770,28 +1710,28 @@
         <v>1673</v>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>26900</v>
+        <v>36000</v>
       </c>
       <c r="AE11" s="10" t="n">
-        <v>4656</v>
+        <v>1435</v>
       </c>
       <c r="AF11" s="10" t="n">
-        <v>33000</v>
+        <v>36000</v>
       </c>
       <c r="AG11" s="10" t="n">
-        <v>44000</v>
+        <v>42000</v>
       </c>
       <c r="AH11" s="10" t="n">
-        <v>26900</v>
+        <v>35700</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>36000</v>
+        <v>38500</v>
       </c>
       <c r="AJ11" s="8" t="n">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="AK11" s="8" t="n">
-        <v>13</v>
+        <v>21.4</v>
       </c>
       <c r="AL11" s="10" t="n">
         <v>40000</v>
@@ -1800,10 +1740,10 @@
         <v>1673</v>
       </c>
       <c r="AN11" s="10" t="n">
-        <v>26900</v>
+        <v>36000</v>
       </c>
       <c r="AO11" s="8" t="n">
-        <v>4656</v>
+        <v>1435</v>
       </c>
       <c r="AP11" s="10" t="inlineStr">
         <is>
@@ -2096,10 +2036,10 @@
         <v>3061</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>34000</v>
+        <v>40000</v>
       </c>
       <c r="Q15" s="10" t="n">
-        <v>2614</v>
+        <v>854</v>
       </c>
       <c r="R15" s="10" t="n">
         <v>40800</v>
@@ -2108,16 +2048,16 @@
         <v>43600</v>
       </c>
       <c r="T15" s="10" t="n">
-        <v>33800</v>
+        <v>37000</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>40000</v>
+        <v>40100</v>
       </c>
       <c r="V15" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>10.7</v>
+        <v>5.9</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>43000</v>
@@ -2126,10 +2066,10 @@
         <v>3061</v>
       </c>
       <c r="Z15" s="10" t="n">
-        <v>34000</v>
+        <v>40000</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>2614</v>
+        <v>854</v>
       </c>
       <c r="AB15" s="10" t="n">
         <v>38000</v>
@@ -2138,10 +2078,10 @@
         <v>1381</v>
       </c>
       <c r="AD15" s="10" t="n">
-        <v>26900</v>
+        <v>37000</v>
       </c>
       <c r="AE15" s="10" t="n">
-        <v>1988</v>
+        <v>1071</v>
       </c>
       <c r="AF15" s="10" t="n">
         <v>37800</v>
@@ -2150,16 +2090,16 @@
         <v>44000</v>
       </c>
       <c r="AH15" s="10" t="n">
-        <v>26900</v>
+        <v>37000</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>36000</v>
+        <v>40000</v>
       </c>
       <c r="AJ15" s="8" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AK15" s="8" t="n">
-        <v>4.7</v>
+        <v>12.7</v>
       </c>
       <c r="AL15" s="10" t="n">
         <v>38000</v>
@@ -2168,10 +2108,10 @@
         <v>1381</v>
       </c>
       <c r="AN15" s="10" t="n">
-        <v>26900</v>
+        <v>37000</v>
       </c>
       <c r="AO15" s="8" t="n">
-        <v>1988</v>
+        <v>1071</v>
       </c>
       <c r="AP15" s="10" t="inlineStr">
         <is>
@@ -2243,10 +2183,10 @@
         <v>4801</v>
       </c>
       <c r="P16" s="10" t="n">
-        <v>34000</v>
+        <v>40000</v>
       </c>
       <c r="Q16" s="10" t="n">
-        <v>2612</v>
+        <v>2209</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>41000</v>
@@ -2255,7 +2195,7 @@
         <v>43600</v>
       </c>
       <c r="T16" s="10" t="n">
-        <v>34000</v>
+        <v>39000</v>
       </c>
       <c r="U16" s="10" t="n">
         <v>40300</v>
@@ -2264,7 +2204,7 @@
         <v>12.5</v>
       </c>
       <c r="W16" s="8" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>43000</v>
@@ -2273,10 +2213,10 @@
         <v>4801</v>
       </c>
       <c r="Z16" s="10" t="n">
-        <v>34000</v>
+        <v>40000</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>2612</v>
+        <v>2209</v>
       </c>
       <c r="AB16" s="10" t="n">
         <v>38000</v>
@@ -2285,10 +2225,10 @@
         <v>1354</v>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>26900</v>
+        <v>38000</v>
       </c>
       <c r="AE16" s="10" t="n">
-        <v>2018</v>
+        <v>1200</v>
       </c>
       <c r="AF16" s="10" t="n">
         <v>37800</v>
@@ -2297,16 +2237,16 @@
         <v>44000</v>
       </c>
       <c r="AH16" s="10" t="n">
-        <v>26900</v>
+        <v>37000</v>
       </c>
       <c r="AI16" s="10" t="n">
-        <v>36000</v>
+        <v>40000</v>
       </c>
       <c r="AJ16" s="8" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AK16" s="8" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="AL16" s="10" t="n">
         <v>38000</v>
@@ -2315,10 +2255,10 @@
         <v>1354</v>
       </c>
       <c r="AN16" s="10" t="n">
-        <v>26900</v>
+        <v>38000</v>
       </c>
       <c r="AO16" s="8" t="n">
-        <v>2018</v>
+        <v>1200</v>
       </c>
       <c r="AP16" s="10" t="inlineStr">
         <is>
@@ -2402,7 +2342,7 @@
         <v>43600</v>
       </c>
       <c r="T17" s="10" t="n">
-        <v>34000</v>
+        <v>40000</v>
       </c>
       <c r="U17" s="10" t="n">
         <v>41200</v>
@@ -2411,7 +2351,7 @@
         <v>7.6</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>43000</v>
@@ -2432,10 +2372,10 @@
         <v>1288</v>
       </c>
       <c r="AD17" s="10" t="n">
-        <v>26900</v>
+        <v>38000</v>
       </c>
       <c r="AE17" s="10" t="n">
-        <v>2215</v>
+        <v>1380</v>
       </c>
       <c r="AF17" s="10" t="n">
         <v>37800</v>
@@ -2444,16 +2384,16 @@
         <v>45000</v>
       </c>
       <c r="AH17" s="10" t="n">
-        <v>26900</v>
+        <v>37500</v>
       </c>
       <c r="AI17" s="10" t="n">
-        <v>38000</v>
+        <v>40000</v>
       </c>
       <c r="AJ17" s="8" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AK17" s="8" t="n">
-        <v>4.7</v>
+        <v>12.8</v>
       </c>
       <c r="AL17" s="10" t="n">
         <v>38000</v>
@@ -2462,10 +2402,10 @@
         <v>1288</v>
       </c>
       <c r="AN17" s="10" t="n">
-        <v>26900</v>
+        <v>38000</v>
       </c>
       <c r="AO17" s="8" t="n">
-        <v>2215</v>
+        <v>1380</v>
       </c>
       <c r="AP17" s="10" t="inlineStr">
         <is>
@@ -2537,10 +2477,10 @@
         <v>196</v>
       </c>
       <c r="P18" s="10" t="n">
-        <v>35000</v>
+        <v>40000</v>
       </c>
       <c r="Q18" s="10" t="n">
-        <v>717</v>
+        <v>397</v>
       </c>
       <c r="R18" s="10" t="n">
         <v>41500</v>
@@ -2549,7 +2489,7 @@
         <v>44900</v>
       </c>
       <c r="T18" s="10" t="n">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="U18" s="10" t="n">
         <v>41000</v>
@@ -2558,7 +2498,7 @@
         <v>6.4</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="X18" s="10" t="n">
         <v>43000</v>
@@ -2567,10 +2507,10 @@
         <v>196</v>
       </c>
       <c r="Z18" s="10" t="n">
-        <v>35000</v>
+        <v>40000</v>
       </c>
       <c r="AA18" s="8" t="n">
-        <v>717</v>
+        <v>397</v>
       </c>
       <c r="AB18" s="10" t="n">
         <v>38000</v>
@@ -2579,28 +2519,28 @@
         <v>1281</v>
       </c>
       <c r="AD18" s="10" t="n">
-        <v>26900</v>
+        <v>38000</v>
       </c>
       <c r="AE18" s="10" t="n">
-        <v>2476</v>
+        <v>1536</v>
       </c>
       <c r="AF18" s="10" t="n">
-        <v>33000</v>
+        <v>37800</v>
       </c>
       <c r="AG18" s="10" t="n">
         <v>45000</v>
       </c>
       <c r="AH18" s="10" t="n">
-        <v>26900</v>
+        <v>37800</v>
       </c>
       <c r="AI18" s="10" t="n">
-        <v>38000</v>
+        <v>40000</v>
       </c>
       <c r="AJ18" s="8" t="n">
-        <v>5.1</v>
+        <v>6.9</v>
       </c>
       <c r="AK18" s="8" t="n">
-        <v>5</v>
+        <v>13.8</v>
       </c>
       <c r="AL18" s="10" t="n">
         <v>38000</v>
@@ -2609,10 +2549,10 @@
         <v>1281</v>
       </c>
       <c r="AN18" s="10" t="n">
-        <v>26900</v>
+        <v>38000</v>
       </c>
       <c r="AO18" s="8" t="n">
-        <v>2476</v>
+        <v>1536</v>
       </c>
       <c r="AP18" s="10" t="inlineStr">
         <is>

--- a/taifex_summary.xlsx
+++ b/taifex_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日摘要" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="每日摘要" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU18"/>
+  <dimension ref="A1:AU25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2575,6 +2575,1035 @@
         <v>1924.83</v>
       </c>
     </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>20593</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>75123</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>-54530</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>-457369690</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>-3398</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>-410259</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>-626176525</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>1770</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>3551</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>181.36</v>
+      </c>
+      <c r="L19" s="10" t="n">
+        <v>88872</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>49004</v>
+      </c>
+      <c r="N19" s="10" t="n">
+        <v>44000</v>
+      </c>
+      <c r="O19" s="10" t="n">
+        <v>688</v>
+      </c>
+      <c r="P19" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="Q19" s="10" t="n">
+        <v>1127</v>
+      </c>
+      <c r="R19" s="10" t="n">
+        <v>42500</v>
+      </c>
+      <c r="S19" s="10" t="n">
+        <v>45500</v>
+      </c>
+      <c r="T19" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="U19" s="10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="X19" s="10" t="n">
+        <v>44000</v>
+      </c>
+      <c r="Y19" s="8" t="n">
+        <v>688</v>
+      </c>
+      <c r="Z19" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AA19" s="8" t="n">
+        <v>1127</v>
+      </c>
+      <c r="AB19" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AC19" s="10" t="n">
+        <v>1272</v>
+      </c>
+      <c r="AD19" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AE19" s="10" t="n">
+        <v>2689</v>
+      </c>
+      <c r="AF19" s="10" t="n">
+        <v>33000</v>
+      </c>
+      <c r="AG19" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="AH19" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AI19" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AJ19" s="8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AK19" s="8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AL19" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AM19" s="8" t="n">
+        <v>1272</v>
+      </c>
+      <c r="AN19" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AO19" s="8" t="n">
+        <v>2689</v>
+      </c>
+      <c r="AP19" s="10" t="inlineStr">
+        <is>
+          <t>短多長空、多頭一致</t>
+        </is>
+      </c>
+      <c r="AQ19" s="9" t="n">
+        <v>-120.85</v>
+      </c>
+      <c r="AR19" s="8" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="AS19" s="9" t="n">
+        <v>-100.37</v>
+      </c>
+      <c r="AT19" s="10" t="n">
+        <v>-201.64</v>
+      </c>
+      <c r="AU19" s="8" t="n">
+        <v>1803.98</v>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/11</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>21382</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>75607</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>-54225</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>-455232088</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>305</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>-426036</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>-639905852</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>3260</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>4073</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>162.33</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>114778</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>70705</v>
+      </c>
+      <c r="N20" s="10" t="n">
+        <v>43500</v>
+      </c>
+      <c r="O20" s="10" t="n">
+        <v>1831</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="Q20" s="10" t="n">
+        <v>2121</v>
+      </c>
+      <c r="R20" s="10" t="n">
+        <v>42400</v>
+      </c>
+      <c r="S20" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="T20" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="U20" s="10" t="n">
+        <v>41500</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="X20" s="10" t="n">
+        <v>43500</v>
+      </c>
+      <c r="Y20" s="8" t="n">
+        <v>1831</v>
+      </c>
+      <c r="Z20" s="10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="AA20" s="8" t="n">
+        <v>2121</v>
+      </c>
+      <c r="AB20" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AC20" s="10" t="n">
+        <v>1272</v>
+      </c>
+      <c r="AD20" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AE20" s="10" t="n">
+        <v>2663</v>
+      </c>
+      <c r="AF20" s="10" t="n">
+        <v>37800</v>
+      </c>
+      <c r="AG20" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AH20" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AI20" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AJ20" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK20" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL20" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AM20" s="8" t="n">
+        <v>1272</v>
+      </c>
+      <c r="AN20" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AO20" s="8" t="n">
+        <v>2663</v>
+      </c>
+      <c r="AP20" s="10" t="inlineStr">
+        <is>
+          <t>短多長空、多頭一致</t>
+        </is>
+      </c>
+      <c r="AQ20" s="9" t="n">
+        <v>-109.84</v>
+      </c>
+      <c r="AR20" s="8" t="n">
+        <v>124.88</v>
+      </c>
+      <c r="AS20" s="8" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="AT20" s="10" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="AU20" s="8" t="n">
+        <v>1024.38</v>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/12</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>22285</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>75357</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>-53072</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>-442759137</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>1153</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>-440250</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>-630476508</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>2902</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>6733</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>161.65</v>
+      </c>
+      <c r="L21" s="10" t="n">
+        <v>135272</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>83681</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="O21" s="10" t="n">
+        <v>2282</v>
+      </c>
+      <c r="P21" s="10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="Q21" s="10" t="n">
+        <v>3466</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>42000</v>
+      </c>
+      <c r="S21" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="T21" s="10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>41700</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="X21" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="Y21" s="8" t="n">
+        <v>2282</v>
+      </c>
+      <c r="Z21" s="10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="AA21" s="8" t="n">
+        <v>3466</v>
+      </c>
+      <c r="AB21" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AC21" s="10" t="n">
+        <v>1962</v>
+      </c>
+      <c r="AD21" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AE21" s="10" t="n">
+        <v>3139</v>
+      </c>
+      <c r="AF21" s="10" t="n">
+        <v>37800</v>
+      </c>
+      <c r="AG21" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AH21" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AI21" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="AJ21" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AK21" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AL21" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AM21" s="8" t="n">
+        <v>1962</v>
+      </c>
+      <c r="AN21" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AO21" s="8" t="n">
+        <v>3139</v>
+      </c>
+      <c r="AP21" s="10" t="inlineStr">
+        <is>
+          <t>短空長多、短多長空</t>
+        </is>
+      </c>
+      <c r="AQ21" s="9" t="n">
+        <v>-304.94</v>
+      </c>
+      <c r="AR21" s="8" t="n">
+        <v>383.17</v>
+      </c>
+      <c r="AS21" s="9" t="n">
+        <v>-206.64</v>
+      </c>
+      <c r="AT21" s="10" t="n">
+        <v>-128.4</v>
+      </c>
+      <c r="AU21" s="8" t="n">
+        <v>679.54</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/13</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>22098</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>74858</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>-52760</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>-437472664</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>312</v>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>-452107</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>-613092850</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>928</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>4559</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>169.31</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>99802</v>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>58946</v>
+      </c>
+      <c r="N22" s="10" t="n">
+        <v>42000</v>
+      </c>
+      <c r="O22" s="10" t="n">
+        <v>6792</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="Q22" s="10" t="n">
+        <v>5587</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <v>41500</v>
+      </c>
+      <c r="S22" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="T22" s="10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="U22" s="10" t="n">
+        <v>41400</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X22" s="10" t="n">
+        <v>42000</v>
+      </c>
+      <c r="Y22" s="8" t="n">
+        <v>6792</v>
+      </c>
+      <c r="Z22" s="10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="AA22" s="8" t="n">
+        <v>5587</v>
+      </c>
+      <c r="AB22" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AC22" s="10" t="n">
+        <v>2160</v>
+      </c>
+      <c r="AD22" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AE22" s="10" t="n">
+        <v>3824</v>
+      </c>
+      <c r="AF22" s="10" t="n">
+        <v>37800</v>
+      </c>
+      <c r="AG22" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AH22" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AI22" s="10" t="n">
+        <v>39000</v>
+      </c>
+      <c r="AJ22" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AK22" s="8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AL22" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AM22" s="8" t="n">
+        <v>2160</v>
+      </c>
+      <c r="AN22" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AO22" s="8" t="n">
+        <v>3824</v>
+      </c>
+      <c r="AP22" s="10" t="inlineStr">
+        <is>
+          <t>短空長多、短多長空</t>
+        </is>
+      </c>
+      <c r="AQ22" s="9" t="n">
+        <v>-434.29</v>
+      </c>
+      <c r="AR22" s="8" t="n">
+        <v>260.62</v>
+      </c>
+      <c r="AS22" s="9" t="n">
+        <v>-302.66</v>
+      </c>
+      <c r="AT22" s="10" t="n">
+        <v>-476.34</v>
+      </c>
+      <c r="AU22" s="9" t="n">
+        <v>-505.8</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>22401</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>73469</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>-51068</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>-425393348</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>1692</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>-461748</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>-610867785</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>1526</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>7766</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>162.46</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>133181</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>81978</v>
+      </c>
+      <c r="N23" s="10" t="n">
+        <v>44700</v>
+      </c>
+      <c r="O23" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="P23" s="10" t="n">
+        <v>39600</v>
+      </c>
+      <c r="Q23" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="R23" s="10" t="n">
+        <v>41700</v>
+      </c>
+      <c r="S23" s="10" t="n">
+        <v>46100</v>
+      </c>
+      <c r="T23" s="10" t="n">
+        <v>37200</v>
+      </c>
+      <c r="U23" s="10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W23" s="8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="X23" s="10" t="n">
+        <v>44700</v>
+      </c>
+      <c r="Y23" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z23" s="10" t="n">
+        <v>39600</v>
+      </c>
+      <c r="AA23" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB23" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AC23" s="10" t="n">
+        <v>2165</v>
+      </c>
+      <c r="AD23" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AE23" s="10" t="n">
+        <v>4201</v>
+      </c>
+      <c r="AF23" s="10" t="n">
+        <v>37800</v>
+      </c>
+      <c r="AG23" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AH23" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AI23" s="10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="AJ23" s="8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AK23" s="8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AL23" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AM23" s="8" t="n">
+        <v>2165</v>
+      </c>
+      <c r="AN23" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AO23" s="8" t="n">
+        <v>4201</v>
+      </c>
+      <c r="AP23" s="10" t="inlineStr">
+        <is>
+          <t>短空長多、短多長空</t>
+        </is>
+      </c>
+      <c r="AQ23" s="8" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="AR23" s="8" t="n">
+        <v>142.96</v>
+      </c>
+      <c r="AS23" s="9" t="n">
+        <v>-12.63</v>
+      </c>
+      <c r="AT23" s="10" t="n">
+        <v>175.76</v>
+      </c>
+      <c r="AU23" s="9" t="n">
+        <v>-924.49</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>20970</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>71933</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>-50963</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>-418268214</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>105</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>-452930</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>-592398798</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>2806</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>8055</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>162.43</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>108147</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>66581</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>44000</v>
+      </c>
+      <c r="O24" s="10" t="n">
+        <v>97</v>
+      </c>
+      <c r="P24" s="10" t="n">
+        <v>37200</v>
+      </c>
+      <c r="Q24" s="10" t="n">
+        <v>229</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>41900</v>
+      </c>
+      <c r="S24" s="10" t="n">
+        <v>46100</v>
+      </c>
+      <c r="T24" s="10" t="n">
+        <v>37200</v>
+      </c>
+      <c r="U24" s="10" t="n">
+        <v>41200</v>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="X24" s="10" t="n">
+        <v>44000</v>
+      </c>
+      <c r="Y24" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z24" s="10" t="n">
+        <v>37200</v>
+      </c>
+      <c r="AA24" s="8" t="n">
+        <v>229</v>
+      </c>
+      <c r="AB24" s="10" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AC24" s="10" t="n">
+        <v>3405</v>
+      </c>
+      <c r="AD24" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AE24" s="10" t="n">
+        <v>5223</v>
+      </c>
+      <c r="AF24" s="10" t="n">
+        <v>37800</v>
+      </c>
+      <c r="AG24" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AH24" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AI24" s="10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="AJ24" s="8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AK24" s="8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AL24" s="10" t="n">
+        <v>46000</v>
+      </c>
+      <c r="AM24" s="8" t="n">
+        <v>3405</v>
+      </c>
+      <c r="AN24" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AO24" s="8" t="n">
+        <v>5223</v>
+      </c>
+      <c r="AP24" s="10" t="inlineStr">
+        <is>
+          <t>短空長多、短多長空</t>
+        </is>
+      </c>
+      <c r="AQ24" s="9" t="n">
+        <v>-104.27</v>
+      </c>
+      <c r="AR24" s="9" t="n">
+        <v>-13.67</v>
+      </c>
+      <c r="AS24" s="9" t="n">
+        <v>-249.43</v>
+      </c>
+      <c r="AT24" s="10" t="n">
+        <v>-367.37</v>
+      </c>
+      <c r="AU24" s="9" t="n">
+        <v>-907.91</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>21791</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>66787</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>-44996</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>-368134053</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>5967</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>-433576</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>-536337133</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>4326</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>8257</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>140.86</v>
+      </c>
+      <c r="L25" s="10" t="n">
+        <v>138277</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>98164</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>44000</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>211</v>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>37000</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>266</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="S25" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="T25" s="10" t="n">
+        <v>37000</v>
+      </c>
+      <c r="U25" s="10" t="n">
+        <v>40200</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="X25" s="10" t="n">
+        <v>44000</v>
+      </c>
+      <c r="Y25" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="Z25" s="10" t="n">
+        <v>37000</v>
+      </c>
+      <c r="AA25" s="8" t="n">
+        <v>266</v>
+      </c>
+      <c r="AB25" s="10" t="n">
+        <v>43500</v>
+      </c>
+      <c r="AC25" s="10" t="n">
+        <v>4708</v>
+      </c>
+      <c r="AD25" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AE25" s="10" t="n">
+        <v>7297</v>
+      </c>
+      <c r="AF25" s="10" t="n">
+        <v>41000</v>
+      </c>
+      <c r="AG25" s="10" t="n">
+        <v>48300</v>
+      </c>
+      <c r="AH25" s="10" t="n">
+        <v>26900</v>
+      </c>
+      <c r="AI25" s="10" t="n">
+        <v>40200</v>
+      </c>
+      <c r="AJ25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK25" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL25" s="10" t="n">
+        <v>43500</v>
+      </c>
+      <c r="AM25" s="8" t="n">
+        <v>4708</v>
+      </c>
+      <c r="AN25" s="10" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AO25" s="8" t="n">
+        <v>7297</v>
+      </c>
+      <c r="AP25" s="10" t="inlineStr">
+        <is>
+          <t>短多長空、多頭一致</t>
+        </is>
+      </c>
+      <c r="AQ25" s="9" t="n">
+        <v>-452.41</v>
+      </c>
+      <c r="AR25" s="8" t="n">
+        <v>166.65</v>
+      </c>
+      <c r="AS25" s="9" t="n">
+        <v>-139.27</v>
+      </c>
+      <c r="AT25" s="10" t="n">
+        <v>-425.03</v>
+      </c>
+      <c r="AU25" s="9" t="n">
+        <v>-1250.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
